--- a/data/pack/eu/colza_hu.xlsx
+++ b/data/pack/eu/colza_hu.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K269"/>
+  <dimension ref="A1:K270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7006,7 +7006,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>418.45</v>
+        <v>387.81</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15229,6 +15229,61 @@
         </is>
       </c>
       <c r="K269" t="inlineStr">
+        <is>
+          <t>Source: European Commission (Agri-food data portal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>colza_hu</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Colza, media nacional (Hungría)</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>542.6</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>tonelada</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>European Commission — Agri-food Data Portal (DG AGRI)</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>EU-REUSE-2011-833</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
         <is>
           <t>Source: European Commission (Agri-food data portal)</t>
         </is>
@@ -15332,7 +15387,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -15343,7 +15398,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9">
@@ -15438,7 +15493,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
